--- a/photography_forms/040_wedding_questionnaire--photography_forms.xlsx
+++ b/photography_forms/040_wedding_questionnaire--photography_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'name',_'value':_'name'}</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'name', 'value': 'Name'}</t>
+          <t>Name</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'email', 'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'phone', 'value': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'photography',_'value':_'photography'}</t>
+          <t>photography</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'photography', 'value': 'Photography'}</t>
+          <t>Photography</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'videography',_'value':_'videography'}</t>
+          <t>videography</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'videography', 'value': 'Videography'}</t>
+          <t>Videography</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'wedding_party',_'value':_'wedding_party'}</t>
+          <t>wedding_party</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'wedding_party', 'value': 'Wedding Party'}</t>
+          <t>Wedding Party</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'online',_'value':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'online', 'value': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'bank_transfer',_'value':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'bank_transfer', 'value': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'cash',_'value':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'cash', 'value': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
